--- a/Matrix CV.xlsx
+++ b/Matrix CV.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10329"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/soutrikbanerjee/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18E8930E-1E32-704B-B8E1-3E0A847E7B03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85E26F8B-CB2B-9846-89AB-1925D38B5925}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="16980" xr2:uid="{2F95C5E4-77A5-A846-975A-1976879AC32A}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="61">
   <si>
     <t>UCB</t>
   </si>
@@ -131,16 +131,7 @@
     <t>Machine Learning</t>
   </si>
   <si>
-    <t>ECA</t>
-  </si>
-  <si>
-    <t>Immunology</t>
-  </si>
-  <si>
     <t>SAS, SQL</t>
-  </si>
-  <si>
-    <t>CTR Data</t>
   </si>
   <si>
     <t>RWE-HEOR, Obs. Data</t>
@@ -232,6 +223,24 @@
   </si>
   <si>
     <t>No. of Projects</t>
+  </si>
+  <si>
+    <t>ECA, TTE</t>
+  </si>
+  <si>
+    <t>RCT Data</t>
+  </si>
+  <si>
+    <t>Resp. Dis., Immunology</t>
+  </si>
+  <si>
+    <t>Adverse Events</t>
+  </si>
+  <si>
+    <t>PRO</t>
+  </si>
+  <si>
+    <t>Biomarkers</t>
   </si>
 </sst>
 </file>
@@ -694,10 +703,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5061A3D-6E5A-F54E-88C1-CE8067317A7C}">
-  <dimension ref="A1:O44"/>
+  <dimension ref="A1:O47"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="19.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.6640625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="6" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="4.83203125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="3.1640625" bestFit="1" customWidth="1"/>
@@ -710,13 +719,13 @@
     <col min="11" max="11" width="6.33203125" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="6.83203125" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="5.83203125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="19.6640625" style="4" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="20.6640625" style="4" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="15" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" s="1" customFormat="1" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>3</v>
@@ -755,15 +764,15 @@
         <v>12</v>
       </c>
       <c r="N1" s="5" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="O1" s="14" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
     </row>
     <row r="2" spans="1:15" ht="17" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B2" s="2">
         <v>10</v>
@@ -802,10 +811,10 @@
         <v>6</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="O2" s="10">
-        <f t="shared" ref="O2:O28" si="0">ROUND(SUM(B2:M2)/12, 1)</f>
+        <f t="shared" ref="O2:O31" si="0">ROUND(SUM(B2:M2)/12, 1)</f>
         <v>10.7</v>
       </c>
     </row>
@@ -1081,7 +1090,7 @@
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="B12" s="3">
         <v>10</v>
@@ -1102,7 +1111,7 @@
       <c r="L12" s="3"/>
       <c r="M12" s="3"/>
       <c r="N12" s="1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="O12" s="10">
         <f t="shared" si="0"/>
@@ -1111,186 +1120,190 @@
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
-        <v>20</v>
+        <v>58</v>
       </c>
       <c r="B13" s="3"/>
-      <c r="C13" s="3"/>
+      <c r="C13" s="3">
+        <v>12</v>
+      </c>
       <c r="D13" s="3"/>
-      <c r="E13" s="3">
-        <v>12</v>
-      </c>
+      <c r="E13" s="3"/>
       <c r="F13" s="3"/>
       <c r="G13" s="3"/>
-      <c r="H13" s="3">
-        <v>3</v>
-      </c>
+      <c r="H13" s="3"/>
       <c r="I13" s="3"/>
       <c r="J13" s="3">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="K13" s="3"/>
       <c r="L13" s="3"/>
-      <c r="M13" s="3">
-        <v>3</v>
-      </c>
+      <c r="M13" s="3"/>
       <c r="N13" s="1" t="s">
-        <v>20</v>
+        <v>58</v>
       </c>
       <c r="O13" s="10">
         <f t="shared" si="0"/>
-        <v>2.2999999999999998</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
-        <v>25</v>
+        <v>59</v>
       </c>
       <c r="B14" s="3"/>
       <c r="C14" s="3"/>
       <c r="D14" s="3"/>
-      <c r="E14" s="3">
-        <v>3</v>
-      </c>
+      <c r="E14" s="3"/>
       <c r="F14" s="3"/>
       <c r="G14" s="3"/>
-      <c r="H14" s="3">
-        <v>3</v>
-      </c>
+      <c r="H14" s="3"/>
       <c r="I14" s="3"/>
-      <c r="J14" s="3"/>
+      <c r="J14" s="3">
+        <v>24</v>
+      </c>
       <c r="K14" s="3"/>
       <c r="L14" s="3"/>
-      <c r="M14" s="3">
-        <v>3</v>
-      </c>
+      <c r="M14" s="3"/>
       <c r="N14" s="1" t="s">
-        <v>25</v>
+        <v>59</v>
       </c>
       <c r="O14" s="10">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
-        <v>21</v>
+        <v>60</v>
       </c>
       <c r="B15" s="3"/>
       <c r="C15" s="3"/>
       <c r="D15" s="3"/>
-      <c r="E15" s="3">
-        <v>12</v>
-      </c>
-      <c r="F15" s="3"/>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3">
+        <v>1</v>
+      </c>
       <c r="G15" s="3"/>
       <c r="H15" s="3"/>
-      <c r="I15" s="3"/>
+      <c r="I15" s="3">
+        <v>1</v>
+      </c>
       <c r="J15" s="3">
-        <v>3</v>
-      </c>
-      <c r="K15" s="3"/>
-      <c r="L15" s="3"/>
+        <v>1</v>
+      </c>
+      <c r="K15" s="3">
+        <v>1</v>
+      </c>
+      <c r="L15" s="3">
+        <v>1</v>
+      </c>
       <c r="M15" s="3"/>
       <c r="N15" s="1" t="s">
-        <v>21</v>
+        <v>60</v>
       </c>
       <c r="O15" s="10">
         <f t="shared" si="0"/>
-        <v>1.3</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="B16" s="3"/>
-      <c r="C16" s="3">
-        <v>16</v>
-      </c>
+      <c r="C16" s="3"/>
       <c r="D16" s="3"/>
-      <c r="E16" s="3"/>
+      <c r="E16" s="3">
+        <v>12</v>
+      </c>
       <c r="F16" s="3"/>
       <c r="G16" s="3"/>
-      <c r="H16" s="3"/>
+      <c r="H16" s="3">
+        <v>3</v>
+      </c>
       <c r="I16" s="3"/>
       <c r="J16" s="3">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="K16" s="3"/>
-      <c r="L16" s="3">
-        <v>1</v>
-      </c>
-      <c r="M16" s="3"/>
+      <c r="L16" s="3"/>
+      <c r="M16" s="3">
+        <v>3</v>
+      </c>
       <c r="N16" s="1" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="O16" s="10">
         <f t="shared" si="0"/>
-        <v>1.6</v>
+        <v>2.2999999999999998</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B17" s="3"/>
       <c r="C17" s="3"/>
-      <c r="D17" s="3">
+      <c r="D17" s="3"/>
+      <c r="E17" s="3">
         <v>3</v>
       </c>
-      <c r="E17" s="3"/>
       <c r="F17" s="3"/>
       <c r="G17" s="3"/>
-      <c r="H17" s="3"/>
+      <c r="H17" s="3">
+        <v>3</v>
+      </c>
       <c r="I17" s="3"/>
-      <c r="J17" s="3">
-        <v>4</v>
-      </c>
+      <c r="J17" s="3"/>
       <c r="K17" s="3"/>
-      <c r="L17" s="3">
-        <v>1</v>
-      </c>
-      <c r="M17" s="3"/>
+      <c r="L17" s="3"/>
+      <c r="M17" s="3">
+        <v>3</v>
+      </c>
       <c r="N17" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="O17" s="10">
         <f t="shared" si="0"/>
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="B18" s="3"/>
       <c r="C18" s="3"/>
-      <c r="D18" s="3">
-        <v>3</v>
-      </c>
-      <c r="E18" s="3"/>
+      <c r="D18" s="3"/>
+      <c r="E18" s="3">
+        <v>12</v>
+      </c>
       <c r="F18" s="3"/>
       <c r="G18" s="3"/>
       <c r="H18" s="3"/>
       <c r="I18" s="3"/>
-      <c r="J18" s="3"/>
+      <c r="J18" s="3">
+        <v>3</v>
+      </c>
       <c r="K18" s="3"/>
       <c r="L18" s="3"/>
       <c r="M18" s="3"/>
       <c r="N18" s="1" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="O18" s="10">
         <f t="shared" si="0"/>
-        <v>0.3</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="B19" s="3"/>
-      <c r="C19" s="3"/>
+      <c r="C19" s="3">
+        <v>16</v>
+      </c>
       <c r="D19" s="3"/>
       <c r="E19" s="3"/>
       <c r="F19" s="3"/>
@@ -1298,512 +1311,596 @@
       <c r="H19" s="3"/>
       <c r="I19" s="3"/>
       <c r="J19" s="3">
-        <v>36</v>
-      </c>
-      <c r="K19" s="3">
-        <v>12</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="K19" s="3"/>
       <c r="L19" s="3">
         <v>1</v>
       </c>
       <c r="M19" s="3"/>
       <c r="N19" s="1" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="O19" s="10">
         <f t="shared" si="0"/>
-        <v>4.0999999999999996</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
-        <v>49</v>
+        <v>26</v>
       </c>
       <c r="B20" s="3"/>
       <c r="C20" s="3"/>
-      <c r="D20" s="3"/>
+      <c r="D20" s="3">
+        <v>3</v>
+      </c>
       <c r="E20" s="3"/>
       <c r="F20" s="3"/>
       <c r="G20" s="3"/>
-      <c r="H20" s="3">
-        <v>3</v>
-      </c>
+      <c r="H20" s="3"/>
       <c r="I20" s="3"/>
-      <c r="J20" s="3"/>
+      <c r="J20" s="3">
+        <v>4</v>
+      </c>
       <c r="K20" s="3"/>
       <c r="L20" s="3">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="M20" s="3"/>
       <c r="N20" s="1" t="s">
-        <v>49</v>
+        <v>26</v>
       </c>
       <c r="O20" s="10">
         <f t="shared" si="0"/>
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="B21" s="3"/>
-      <c r="C21" s="3">
-        <v>21</v>
-      </c>
-      <c r="D21" s="3"/>
+      <c r="C21" s="3"/>
+      <c r="D21" s="3">
+        <v>3</v>
+      </c>
       <c r="E21" s="3"/>
       <c r="F21" s="3"/>
-      <c r="G21" s="3">
-        <v>5</v>
-      </c>
+      <c r="G21" s="3"/>
       <c r="H21" s="3"/>
       <c r="I21" s="3"/>
       <c r="J21" s="3"/>
       <c r="K21" s="3"/>
-      <c r="L21" s="3">
-        <v>8</v>
-      </c>
+      <c r="L21" s="3"/>
       <c r="M21" s="3"/>
       <c r="N21" s="1" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="O21" s="10">
         <f t="shared" si="0"/>
-        <v>2.8</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="B22" s="3"/>
-      <c r="C22" s="3">
-        <v>12</v>
-      </c>
+      <c r="C22" s="3"/>
       <c r="D22" s="3"/>
       <c r="E22" s="3"/>
-      <c r="F22" s="3">
-        <v>23</v>
-      </c>
+      <c r="F22" s="3"/>
       <c r="G22" s="3"/>
       <c r="H22" s="3"/>
-      <c r="I22" s="3">
-        <v>11</v>
-      </c>
-      <c r="J22" s="3"/>
-      <c r="K22" s="3"/>
-      <c r="L22" s="3"/>
+      <c r="I22" s="3"/>
+      <c r="J22" s="3">
+        <v>36</v>
+      </c>
+      <c r="K22" s="3">
+        <v>12</v>
+      </c>
+      <c r="L22" s="3">
+        <v>1</v>
+      </c>
       <c r="M22" s="3"/>
       <c r="N22" s="1" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="O22" s="10">
         <f t="shared" si="0"/>
-        <v>3.8</v>
+        <v>4.0999999999999996</v>
       </c>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B23" s="3">
-        <v>10</v>
-      </c>
-      <c r="C23" s="3">
-        <v>27</v>
-      </c>
+        <v>46</v>
+      </c>
+      <c r="B23" s="3"/>
+      <c r="C23" s="3"/>
       <c r="D23" s="3"/>
-      <c r="E23" s="3">
-        <v>6</v>
-      </c>
-      <c r="F23" s="3">
-        <v>47</v>
-      </c>
-      <c r="G23" s="3">
-        <v>5</v>
-      </c>
-      <c r="H23" s="3"/>
-      <c r="I23" s="3">
-        <v>4</v>
-      </c>
+      <c r="E23" s="3"/>
+      <c r="F23" s="3"/>
+      <c r="G23" s="3"/>
+      <c r="H23" s="3">
+        <v>3</v>
+      </c>
+      <c r="I23" s="3"/>
       <c r="J23" s="3"/>
-      <c r="K23" s="3">
-        <v>6</v>
-      </c>
+      <c r="K23" s="3"/>
       <c r="L23" s="3">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="M23" s="3"/>
       <c r="N23" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="O23" s="11">
-        <f t="shared" si="0"/>
-        <v>10.7</v>
+        <v>46</v>
+      </c>
+      <c r="O23" s="10">
+        <f t="shared" si="0"/>
+        <v>1.4</v>
       </c>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="B24" s="3"/>
       <c r="C24" s="3">
-        <v>6</v>
-      </c>
-      <c r="D24" s="3">
-        <v>3</v>
-      </c>
-      <c r="E24" s="3">
-        <v>6</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="D24" s="3"/>
+      <c r="E24" s="3"/>
       <c r="F24" s="3"/>
-      <c r="G24" s="3"/>
-      <c r="H24" s="3">
-        <v>6</v>
-      </c>
-      <c r="I24" s="3">
-        <v>7</v>
-      </c>
-      <c r="J24" s="3">
-        <v>46</v>
-      </c>
-      <c r="K24" s="3">
-        <v>6</v>
-      </c>
-      <c r="L24" s="3"/>
+      <c r="G24" s="3">
+        <v>5</v>
+      </c>
+      <c r="H24" s="3"/>
+      <c r="I24" s="3"/>
+      <c r="J24" s="3"/>
+      <c r="K24" s="3"/>
+      <c r="L24" s="3">
+        <v>8</v>
+      </c>
       <c r="M24" s="3"/>
       <c r="N24" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="O24" s="11">
-        <f t="shared" si="0"/>
-        <v>6.7</v>
+        <v>23</v>
+      </c>
+      <c r="O24" s="10">
+        <f t="shared" si="0"/>
+        <v>2.8</v>
       </c>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
-        <v>28</v>
+        <v>57</v>
       </c>
       <c r="B25" s="3"/>
-      <c r="C25" s="3"/>
+      <c r="C25" s="3">
+        <v>12</v>
+      </c>
       <c r="D25" s="3"/>
       <c r="E25" s="3"/>
-      <c r="F25" s="3"/>
+      <c r="F25" s="3">
+        <v>25</v>
+      </c>
       <c r="G25" s="3"/>
       <c r="H25" s="3"/>
-      <c r="I25" s="3"/>
-      <c r="J25" s="3">
-        <v>46</v>
-      </c>
+      <c r="I25" s="3">
+        <v>11</v>
+      </c>
+      <c r="J25" s="3"/>
       <c r="K25" s="3"/>
       <c r="L25" s="3"/>
       <c r="M25" s="3"/>
       <c r="N25" s="1" t="s">
-        <v>28</v>
+        <v>57</v>
       </c>
       <c r="O25" s="10">
         <f t="shared" si="0"/>
-        <v>3.8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B26" s="3"/>
-      <c r="C26" s="3"/>
+        <v>32</v>
+      </c>
+      <c r="B26" s="3">
+        <v>10</v>
+      </c>
+      <c r="C26" s="3">
+        <v>27</v>
+      </c>
       <c r="D26" s="3"/>
-      <c r="E26" s="3"/>
-      <c r="F26" s="3"/>
-      <c r="G26" s="3"/>
+      <c r="E26" s="3">
+        <v>6</v>
+      </c>
+      <c r="F26" s="3">
+        <v>47</v>
+      </c>
+      <c r="G26" s="3">
+        <v>5</v>
+      </c>
       <c r="H26" s="3"/>
-      <c r="I26" s="3"/>
+      <c r="I26" s="3">
+        <v>4</v>
+      </c>
       <c r="J26" s="3"/>
       <c r="K26" s="3">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="L26" s="3">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="M26" s="3"/>
       <c r="N26" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="O26" s="10">
-        <f t="shared" si="0"/>
-        <v>1.3</v>
+        <v>32</v>
+      </c>
+      <c r="O26" s="11">
+        <f t="shared" si="0"/>
+        <v>10.7</v>
       </c>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
-        <v>36</v>
+        <v>56</v>
       </c>
       <c r="B27" s="3"/>
-      <c r="C27" s="3"/>
-      <c r="D27" s="3"/>
-      <c r="E27" s="3"/>
+      <c r="C27" s="3">
+        <v>6</v>
+      </c>
+      <c r="D27" s="3">
+        <v>3</v>
+      </c>
+      <c r="E27" s="3">
+        <v>6</v>
+      </c>
       <c r="F27" s="3"/>
       <c r="G27" s="3"/>
-      <c r="H27" s="3"/>
-      <c r="I27" s="3"/>
-      <c r="J27" s="3"/>
-      <c r="K27" s="3"/>
+      <c r="H27" s="3">
+        <v>6</v>
+      </c>
+      <c r="I27" s="3">
+        <v>7</v>
+      </c>
+      <c r="J27" s="3">
+        <v>46</v>
+      </c>
+      <c r="K27" s="3">
+        <v>6</v>
+      </c>
       <c r="L27" s="3"/>
-      <c r="M27" s="3">
+      <c r="M27" s="3"/>
+      <c r="N27" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="O27" s="11">
+        <f t="shared" si="0"/>
+        <v>6.7</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A28" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B28" s="3"/>
+      <c r="C28" s="3"/>
+      <c r="D28" s="3"/>
+      <c r="E28" s="3"/>
+      <c r="F28" s="3"/>
+      <c r="G28" s="3"/>
+      <c r="H28" s="3"/>
+      <c r="I28" s="3"/>
+      <c r="J28" s="3">
+        <v>46</v>
+      </c>
+      <c r="K28" s="3"/>
+      <c r="L28" s="3"/>
+      <c r="M28" s="3"/>
+      <c r="N28" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="O28" s="10">
+        <f t="shared" si="0"/>
+        <v>3.8</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A29" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B29" s="3"/>
+      <c r="C29" s="3"/>
+      <c r="D29" s="3"/>
+      <c r="E29" s="3"/>
+      <c r="F29" s="3"/>
+      <c r="G29" s="3"/>
+      <c r="H29" s="3"/>
+      <c r="I29" s="3"/>
+      <c r="J29" s="3"/>
+      <c r="K29" s="3">
+        <v>12</v>
+      </c>
+      <c r="L29" s="3">
+        <v>4</v>
+      </c>
+      <c r="M29" s="3"/>
+      <c r="N29" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="O29" s="10">
+        <f t="shared" si="0"/>
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A30" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B30" s="3"/>
+      <c r="C30" s="3"/>
+      <c r="D30" s="3"/>
+      <c r="E30" s="3"/>
+      <c r="F30" s="3"/>
+      <c r="G30" s="3"/>
+      <c r="H30" s="3"/>
+      <c r="I30" s="3"/>
+      <c r="J30" s="3"/>
+      <c r="K30" s="3"/>
+      <c r="L30" s="3"/>
+      <c r="M30" s="3">
         <v>1</v>
       </c>
-      <c r="N27" s="1" t="s">
+      <c r="N30" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="O30" s="10">
+        <f t="shared" si="0"/>
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="B31" s="7"/>
+      <c r="C31" s="7"/>
+      <c r="D31" s="7"/>
+      <c r="E31" s="7"/>
+      <c r="F31" s="7">
+        <v>18</v>
+      </c>
+      <c r="G31" s="7"/>
+      <c r="H31" s="7"/>
+      <c r="I31" s="7">
+        <v>5</v>
+      </c>
+      <c r="J31" s="7"/>
+      <c r="K31" s="7"/>
+      <c r="L31" s="7"/>
+      <c r="M31" s="7">
+        <v>12</v>
+      </c>
+      <c r="N31" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="O31" s="12">
+        <f t="shared" si="0"/>
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="B32" s="9">
+        <v>10</v>
+      </c>
+      <c r="C32" s="9">
+        <v>33</v>
+      </c>
+      <c r="D32" s="9">
+        <v>3</v>
+      </c>
+      <c r="E32" s="9">
+        <v>12</v>
+      </c>
+      <c r="F32" s="9">
+        <v>47</v>
+      </c>
+      <c r="G32" s="9">
+        <v>5</v>
+      </c>
+      <c r="H32" s="9">
+        <v>6</v>
+      </c>
+      <c r="I32" s="9">
+        <v>11</v>
+      </c>
+      <c r="J32" s="9">
+        <v>46</v>
+      </c>
+      <c r="K32" s="9">
+        <v>12</v>
+      </c>
+      <c r="L32" s="9">
+        <v>23</v>
+      </c>
+      <c r="M32" s="9">
+        <v>46</v>
+      </c>
+      <c r="N32" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="O32" s="13">
+        <f>ROUND(SUM(B32:L32)/12, 1)</f>
+        <v>17.3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="B33" s="9">
+        <v>240</v>
+      </c>
+      <c r="C33" s="9">
+        <v>50</v>
+      </c>
+      <c r="D33" s="9">
+        <v>15</v>
+      </c>
+      <c r="E33" s="9">
+        <v>72</v>
+      </c>
+      <c r="F33" s="9">
+        <v>58</v>
+      </c>
+      <c r="G33" s="9">
+        <v>75</v>
+      </c>
+      <c r="H33" s="9">
+        <v>60</v>
+      </c>
+      <c r="I33" s="9">
+        <v>66</v>
+      </c>
+      <c r="J33" s="9">
+        <v>45</v>
+      </c>
+      <c r="K33" s="9">
+        <v>45</v>
+      </c>
+      <c r="L33" s="9">
+        <v>66</v>
+      </c>
+      <c r="M33" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N33" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="O33" s="15">
+        <f>ROUND(O32*365/O34, 0)</f>
+        <v>54</v>
+      </c>
+    </row>
+    <row r="34" spans="1:15" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B34" s="6">
+        <v>1</v>
+      </c>
+      <c r="C34" s="6">
+        <v>20</v>
+      </c>
+      <c r="D34" s="6">
+        <v>6</v>
+      </c>
+      <c r="E34" s="6">
+        <v>5</v>
+      </c>
+      <c r="F34" s="6">
+        <v>25</v>
+      </c>
+      <c r="G34" s="6">
+        <v>2</v>
+      </c>
+      <c r="H34" s="6">
+        <v>3</v>
+      </c>
+      <c r="I34" s="6">
+        <v>5</v>
+      </c>
+      <c r="J34" s="6">
+        <v>32</v>
+      </c>
+      <c r="K34" s="6">
+        <v>8</v>
+      </c>
+      <c r="L34" s="6">
+        <v>10</v>
+      </c>
+      <c r="M34" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="N34" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="O34" s="12">
+        <f>SUM(B34:L34)</f>
+        <v>117</v>
+      </c>
+    </row>
+    <row r="35" spans="1:15" ht="17" thickTop="1" x14ac:dyDescent="0.2">
+      <c r="B35" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="36" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="B36" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="37" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="B37" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="38" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="B38" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="39" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="B39" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="40" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="B40" t="s">
         <v>36</v>
       </c>
-      <c r="O27" s="10">
-        <f t="shared" si="0"/>
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:15" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="B28" s="7"/>
-      <c r="C28" s="7"/>
-      <c r="D28" s="7"/>
-      <c r="E28" s="7"/>
-      <c r="F28" s="7">
-        <v>18</v>
-      </c>
-      <c r="G28" s="7"/>
-      <c r="H28" s="7"/>
-      <c r="I28" s="7">
-        <v>5</v>
-      </c>
-      <c r="J28" s="7"/>
-      <c r="K28" s="7"/>
-      <c r="L28" s="7"/>
-      <c r="M28" s="7">
-        <v>12</v>
-      </c>
-      <c r="N28" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="O28" s="12">
-        <f t="shared" si="0"/>
-        <v>2.9</v>
-      </c>
-    </row>
-    <row r="29" spans="1:15" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="B29" s="9">
-        <v>10</v>
-      </c>
-      <c r="C29" s="9">
-        <v>33</v>
-      </c>
-      <c r="D29" s="9">
-        <v>3</v>
-      </c>
-      <c r="E29" s="9">
-        <v>12</v>
-      </c>
-      <c r="F29" s="9">
-        <v>47</v>
-      </c>
-      <c r="G29" s="9">
-        <v>5</v>
-      </c>
-      <c r="H29" s="9">
-        <v>6</v>
-      </c>
-      <c r="I29" s="9">
-        <v>11</v>
-      </c>
-      <c r="J29" s="9">
-        <v>46</v>
-      </c>
-      <c r="K29" s="9">
-        <v>12</v>
-      </c>
-      <c r="L29" s="9">
-        <v>23</v>
-      </c>
-      <c r="M29" s="9">
-        <v>46</v>
-      </c>
-      <c r="N29" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="O29" s="13">
-        <f>ROUND(SUM(B29:L29)/12, 1)</f>
-        <v>17.3</v>
-      </c>
-    </row>
-    <row r="30" spans="1:15" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="8" t="s">
+    </row>
+    <row r="41" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="B41" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="42" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="B42" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="43" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="B43" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="44" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="B44" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="45" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="B45" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="46" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="B46" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="47" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="B47" t="s">
         <v>52</v>
-      </c>
-      <c r="B30" s="9">
-        <v>240</v>
-      </c>
-      <c r="C30" s="9">
-        <v>50</v>
-      </c>
-      <c r="D30" s="9">
-        <v>15</v>
-      </c>
-      <c r="E30" s="9">
-        <v>72</v>
-      </c>
-      <c r="F30" s="9">
-        <v>58</v>
-      </c>
-      <c r="G30" s="9">
-        <v>75</v>
-      </c>
-      <c r="H30" s="9">
-        <v>60</v>
-      </c>
-      <c r="I30" s="9">
-        <v>66</v>
-      </c>
-      <c r="J30" s="9">
-        <v>45</v>
-      </c>
-      <c r="K30" s="9">
-        <v>45</v>
-      </c>
-      <c r="L30" s="9">
-        <v>66</v>
-      </c>
-      <c r="M30" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="N30" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="O30" s="15">
-        <f>ROUND(O29*365/O31, 0)</f>
-        <v>54</v>
-      </c>
-    </row>
-    <row r="31" spans="1:15" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="B31" s="6">
-        <v>1</v>
-      </c>
-      <c r="C31" s="6">
-        <v>20</v>
-      </c>
-      <c r="D31" s="6">
-        <v>6</v>
-      </c>
-      <c r="E31" s="6">
-        <v>5</v>
-      </c>
-      <c r="F31" s="6">
-        <v>25</v>
-      </c>
-      <c r="G31" s="6">
-        <v>2</v>
-      </c>
-      <c r="H31" s="6">
-        <v>3</v>
-      </c>
-      <c r="I31" s="6">
-        <v>5</v>
-      </c>
-      <c r="J31" s="6">
-        <v>32</v>
-      </c>
-      <c r="K31" s="6">
-        <v>8</v>
-      </c>
-      <c r="L31" s="6">
-        <v>10</v>
-      </c>
-      <c r="M31" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="N31" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="O31" s="12">
-        <f>SUM(B31:L31)</f>
-        <v>117</v>
-      </c>
-    </row>
-    <row r="32" spans="1:15" ht="17" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="B32" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="33" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B33" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="34" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B34" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="35" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B35" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="36" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B36" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="37" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B37" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="38" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B38" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="39" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B39" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="40" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B40" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="41" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B41" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="42" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B42" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="43" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B43" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="44" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B44" t="s">
-        <v>55</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="O29" formulaRange="1"/>
+    <ignoredError sqref="O32" formulaRange="1"/>
   </ignoredErrors>
 </worksheet>
 </file>